--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117631263</v>
+        <v>117631874</v>
       </c>
       <c r="B2" t="n">
-        <v>96791</v>
+        <v>94250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339365</v>
+        <v>339337</v>
       </c>
       <c r="R2" t="n">
-        <v>6424573</v>
+        <v>6424443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bestånd vid skogsbäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117631338</v>
+        <v>117632041</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57303</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +904,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -933,7 +928,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339382</v>
+        <v>339413</v>
       </c>
       <c r="R4" t="n">
-        <v>6424551</v>
+        <v>6424353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117631729</v>
+        <v>117632018</v>
       </c>
       <c r="B5" t="n">
         <v>57303</v>
@@ -1041,7 +1040,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1051,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339425</v>
+        <v>339326</v>
       </c>
       <c r="R5" t="n">
-        <v>6424501</v>
+        <v>6424326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117631933</v>
+        <v>117631338</v>
       </c>
       <c r="B6" t="n">
-        <v>57303</v>
+        <v>57656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,20 +1124,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339357</v>
+        <v>339382</v>
       </c>
       <c r="R6" t="n">
-        <v>6424390</v>
+        <v>6424551</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,11 +1192,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår av spillkråka på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1218,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117632018</v>
+        <v>117631933</v>
       </c>
       <c r="B7" t="n">
         <v>57303</v>
@@ -1260,11 +1254,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1272,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339326</v>
+        <v>339357</v>
       </c>
       <c r="R7" t="n">
-        <v>6424326</v>
+        <v>6424390</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,6 +1298,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117631072</v>
+        <v>117631729</v>
       </c>
       <c r="B8" t="n">
-        <v>94250</v>
+        <v>57303</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,31 +1341,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339395</v>
+        <v>339425</v>
       </c>
       <c r="R8" t="n">
-        <v>6424590</v>
+        <v>6424501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1421,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1441,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117631874</v>
+        <v>117631263</v>
       </c>
       <c r="B9" t="n">
-        <v>94250</v>
+        <v>96791</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339337</v>
+        <v>339365</v>
       </c>
       <c r="R9" t="n">
-        <v>6424443</v>
+        <v>6424573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,6 +1519,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bestånd vid skogsbäck</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117632041</v>
+        <v>117631072</v>
       </c>
       <c r="B10" t="n">
-        <v>57303</v>
+        <v>94250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,35 +1563,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1596,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339413</v>
+        <v>339395</v>
       </c>
       <c r="R10" t="n">
-        <v>6424353</v>
+        <v>6424590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,6 +1639,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117821516</v>
+        <v>117821561</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>94610</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,42 +1670,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1714,13 +1710,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339363</v>
+        <v>339472</v>
       </c>
       <c r="R11" t="n">
-        <v>6424376</v>
+        <v>6424341</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117821561</v>
+        <v>117821516</v>
       </c>
       <c r="B13" t="n">
-        <v>94610</v>
+        <v>97836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,38 +1924,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339472</v>
+        <v>339363</v>
       </c>
       <c r="R13" t="n">
-        <v>6424341</v>
+        <v>6424376</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117827529</v>
+        <v>117827506</v>
       </c>
       <c r="B14" t="n">
         <v>57303</v>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>339359</v>
+        <v>339364</v>
       </c>
       <c r="R14" t="n">
-        <v>6424363</v>
+        <v>6424475</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117827506</v>
+        <v>117827514</v>
       </c>
       <c r="B16" t="n">
         <v>57303</v>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>339364</v>
+        <v>339359</v>
       </c>
       <c r="R16" t="n">
-        <v>6424475</v>
+        <v>6424363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117822857</v>
+        <v>117822864</v>
       </c>
       <c r="B18" t="n">
-        <v>57303</v>
+        <v>94610</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,35 +2523,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2603,6 +2599,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2621,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117822864</v>
+        <v>117822857</v>
       </c>
       <c r="B19" t="n">
-        <v>94610</v>
+        <v>57303</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,31 +2630,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2709,7 +2710,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2833,6 +2833,131 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118098391</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ale Ramstorp berget, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>339380</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6424370</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kilanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117631874</v>
+        <v>117631338</v>
       </c>
       <c r="B2" t="n">
-        <v>94250</v>
+        <v>57657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339337</v>
+        <v>339382</v>
       </c>
       <c r="R2" t="n">
-        <v>6424443</v>
+        <v>6424551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117631830</v>
+        <v>117632041</v>
       </c>
       <c r="B3" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,7 +819,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339393</v>
+        <v>339413</v>
       </c>
       <c r="R3" t="n">
-        <v>6424424</v>
+        <v>6424353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117632041</v>
+        <v>117631729</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339413</v>
+        <v>339425</v>
       </c>
       <c r="R4" t="n">
-        <v>6424353</v>
+        <v>6424501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1004,7 @@
         <v>117632018</v>
       </c>
       <c r="B5" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117631338</v>
+        <v>117631874</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>94252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,27 +1127,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339382</v>
+        <v>339337</v>
       </c>
       <c r="R6" t="n">
-        <v>6424551</v>
+        <v>6424443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117631933</v>
+        <v>117631830</v>
       </c>
       <c r="B7" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,7 +1254,11 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339357</v>
+        <v>339393</v>
       </c>
       <c r="R7" t="n">
-        <v>6424390</v>
+        <v>6424424</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,11 +1302,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår av spillkråka på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117631729</v>
+        <v>117631933</v>
       </c>
       <c r="B8" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,11 +1364,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1377,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339425</v>
+        <v>339357</v>
       </c>
       <c r="R8" t="n">
-        <v>6424501</v>
+        <v>6424390</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1408,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
         <v>117631263</v>
       </c>
       <c r="B9" t="n">
-        <v>96791</v>
+        <v>96793</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>117631072</v>
       </c>
       <c r="B10" t="n">
-        <v>94250</v>
+        <v>94252</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117821561</v>
+        <v>117821460</v>
       </c>
       <c r="B11" t="n">
-        <v>94610</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,38 +1670,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1710,13 +1714,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339472</v>
+        <v>339352</v>
       </c>
       <c r="R11" t="n">
-        <v>6424341</v>
+        <v>6424519</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117821460</v>
+        <v>117821516</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,7 +1822,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1839,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339352</v>
+        <v>339363</v>
       </c>
       <c r="R12" t="n">
-        <v>6424519</v>
+        <v>6424376</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,7 +1878,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117821516</v>
+        <v>117821561</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>94612</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,42 +1928,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339363</v>
+        <v>339472</v>
       </c>
       <c r="R13" t="n">
-        <v>6424376</v>
+        <v>6424341</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117827506</v>
+        <v>117827559</v>
       </c>
       <c r="B14" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>339364</v>
+        <v>339359</v>
       </c>
       <c r="R14" t="n">
-        <v>6424475</v>
+        <v>6424363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>117827486</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117827514</v>
+        <v>117827506</v>
       </c>
       <c r="B16" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>339359</v>
+        <v>339364</v>
       </c>
       <c r="R16" t="n">
-        <v>6424363</v>
+        <v>6424475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
         <v>117962584</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117822864</v>
+        <v>117822856</v>
       </c>
       <c r="B18" t="n">
-        <v>94610</v>
+        <v>94252</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2555,13 +2555,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>339461</v>
+        <v>339398</v>
       </c>
       <c r="R18" t="n">
-        <v>6424328</v>
+        <v>6424433</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117822857</v>
+        <v>117822864</v>
       </c>
       <c r="B19" t="n">
-        <v>57303</v>
+        <v>94612</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,35 +2630,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2710,6 +2706,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2728,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117822856</v>
+        <v>117822857</v>
       </c>
       <c r="B20" t="n">
-        <v>94250</v>
+        <v>57304</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,31 +2737,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2772,13 +2773,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>339398</v>
+        <v>339461</v>
       </c>
       <c r="R20" t="n">
-        <v>6424433</v>
+        <v>6424328</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2816,7 +2817,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2958,6 +2958,118 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121592550</v>
+      </c>
+      <c r="B22" t="n">
+        <v>94517</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ramstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>339333</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6424519</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kilanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Vanligt förekommande i stort område</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94525</v>
+        <v>94543</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94543</v>
+        <v>94545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94545</v>
+        <v>94552</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94552</v>
+        <v>94561</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94587</v>
+        <v>94597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94597</v>
+        <v>94609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94609</v>
+        <v>94614</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 17566-2024 artfynd.xlsx
+++ b/artfynd/A 17566-2024 artfynd.xlsx
@@ -2963,7 +2963,7 @@
         <v>121592550</v>
       </c>
       <c r="B22" t="n">
-        <v>94614</v>
+        <v>94623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,11 +2977,6 @@
       </c>
       <c r="E22" t="n">
         <v>2810</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa</t>
-        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
